--- a/extra-wishlist.xlsx
+++ b/extra-wishlist.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{B4B05395-9F9B-49FF-811B-A317F2978A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{152F7F1F-8A0F-4DEF-BB8B-0A7A4A89E215}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506A20C0-5A7A-4C5A-B5B8-F2B902A2B820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Extra Wishlist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="125">
   <si>
     <t>Image</t>
   </si>
@@ -203,9 +203,6 @@
     <t>Sigma 24-70mm f/2.8 DG DN II Art</t>
   </si>
   <si>
-    <t>https://static01.galaxus.com/productimages/3/4/1/4/6/9/1/6/1/2/1/6/6/2/2/1/8/4/9/682182dc-69c0-4397-b129-6fef5b7c1b49_cropped.jpg_2880.avif</t>
-  </si>
-  <si>
     <t>Sigma 100-400mm f/5.0-6.3 DG DN OS, Sony E</t>
   </si>
   <si>
@@ -264,12 +261,168 @@
   </si>
   <si>
     <t>ELAC Uni-Fi UF52 (1 Pair)</t>
+  </si>
+  <si>
+    <t>https://shop.visuals.ch/en/led-panel/1076633-amaran---ace-25c-silver-kit.html</t>
+  </si>
+  <si>
+    <t>132 CHF</t>
+  </si>
+  <si>
+    <t>Amaran COB 60x S</t>
+  </si>
+  <si>
+    <t>Amaran Ace 25c Silver Kit</t>
+  </si>
+  <si>
+    <t>https://static.bhphoto.com/images/multiple_images/images1000x1000/1677666925_IMG_1947318.jpg</t>
+  </si>
+  <si>
+    <t>https://shop.visuals.ch/en/led-fixture/1060763-amaran-cob-60x-s-eu-version.html</t>
+  </si>
+  <si>
+    <t>172 CHF</t>
+  </si>
+  <si>
+    <t>https://static.bhphoto.com/images/multiple_images/images750x750/1729007191_IMG_2357582.jpg</t>
+  </si>
+  <si>
+    <t>BenQ Screenbar Halo 2</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/1/1/4/9/7/3/0/0/5/9/4/8/1/2/1/3/5/0/6/019a267c-c52a-7e01-b9f8-c15e936c5316_2880.avif</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/benq-screenbar-halo-2-monitor-light-bars-58551471</t>
+  </si>
+  <si>
+    <t>159 CHF</t>
+  </si>
+  <si>
+    <t>1200 CHF</t>
+  </si>
+  <si>
+    <t>400 CHF</t>
+  </si>
+  <si>
+    <t>700 CHF</t>
+  </si>
+  <si>
+    <t>Cullmann Carvao 816TCS</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/7/8/4/7/6/6/2/6/7/1/5/4/0/3/8/6/1/1/4/0199edae-f4d0-708d-b991-1a9153acedf6_2880.avif</t>
+  </si>
+  <si>
+    <t>60 CHF</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/cullmann-carvao-816tcs-metal-carbon-tripod-10715255</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/4/0/1/3/1/3/1/8/1/9/2/3/7/2/7/7/5/1/5/0199e7cf-6f32-7b15-9569-35d3d36a3f0e_2880.avif</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/xrite-calibrite-colorchecker-passport-video-2-14-cm-1-cm-background-systems-39132613</t>
+  </si>
+  <si>
+    <t>Xrite Calibrite ColorChecker Passport Video 2</t>
+  </si>
+  <si>
+    <t>112 CHF</t>
+  </si>
+  <si>
+    <t>Sony FE 100mm F2.8 Macro GM</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/3/7/4/9/3/3/5/1/3/8/8/6/4/6/8/1/1/6/6/019a27d5-43c4-76b8-8e04-b14c2a9debc5_2880.avif</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/sony-fe-100mm-f28-macro-gm-sony-e-full-size-lenses-62486907</t>
+  </si>
+  <si>
+    <t>1500 CHF</t>
+  </si>
+  <si>
+    <t>1020 CHF</t>
+  </si>
+  <si>
+    <t>870 CHF</t>
+  </si>
+  <si>
+    <t>1236 CHF</t>
+  </si>
+  <si>
+    <t>3800 CHF</t>
+  </si>
+  <si>
+    <t>1160 CHF</t>
+  </si>
+  <si>
+    <t>Anker Prime</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/4/8/3/7/5/9/8/8/2/3/9/9/0/3/6/1/7/3/4/d6111992-19ea-4948-872a-1fd969756faa_cropped.jpg_2880.avif</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/anker-prime-27650-mah-250-w-9954-wh-powerbanks-40773021</t>
+  </si>
+  <si>
+    <t>160 CHF</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/dell-ultrasharp-u4025qw-5120-x-2160-pixels-40-monitor-43336912</t>
+  </si>
+  <si>
+    <t>1300 CHF</t>
+  </si>
+  <si>
+    <t>750 CHF</t>
+  </si>
+  <si>
+    <t>1700 CHF</t>
+  </si>
+  <si>
+    <t>240 CHF</t>
+  </si>
+  <si>
+    <t>250 CHF</t>
+  </si>
+  <si>
+    <t>540 CHF</t>
+  </si>
+  <si>
+    <t>45 CHF</t>
+  </si>
+  <si>
+    <t>1600 CHF</t>
+  </si>
+  <si>
+    <t>330 CHF</t>
+  </si>
+  <si>
+    <t>220 CHF</t>
+  </si>
+  <si>
+    <t>520 CHF</t>
+  </si>
+  <si>
+    <t>Dell UltraSharp U4025QW</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/8/6/4/3/4/3/1/9/2/8/8/6/0/0/7/1/4/4/1/7daab532-1db1-4c0a-86f9-057b86bbe861_cropped.jpg_2880.avif</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/5/6/5/6/4/4/1/6/1/8/4/0/4/2/2/5/3/6/3/aa1c795f-247e-4e96-9a96-bdded01c865b_cropped.jpg_2880.avif</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -322,10 +475,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -641,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.140625" customWidth="1"/>
@@ -668,21 +822,21 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
         <v>59</v>
       </c>
-      <c r="B3" t="s">
-        <v>60</v>
-      </c>
       <c r="C3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3">
-        <v>400</v>
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -695,360 +849,500 @@
       <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4">
-        <v>700</v>
+      <c r="D4" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>1200</v>
+        <v>81</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7">
-        <v>1160</v>
+        <v>79</v>
+      </c>
+      <c r="D7" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8">
-        <v>160</v>
+      <c r="E8" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E9" t="s">
-        <v>67</v>
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10">
-        <v>3800</v>
+      <c r="E10" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11">
-        <v>1236</v>
+        <v>84</v>
+      </c>
+      <c r="D11" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12">
-        <v>870</v>
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13">
-        <v>1020</v>
+        <v>95</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E14" t="s">
-        <v>67</v>
+      <c r="A14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15">
-        <v>45</v>
+      <c r="E15" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16">
-        <v>45</v>
+        <v>124</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E17" t="s">
-        <v>67</v>
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="3">
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18">
-        <v>540</v>
+      <c r="E18" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19">
-        <v>250</v>
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20">
-        <v>240</v>
+        <v>65</v>
+      </c>
+      <c r="D20" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21">
-        <v>240</v>
+        <v>56</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" t="s">
-        <v>44</v>
+        <v>70</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22">
-        <v>1700</v>
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E23" t="s">
-        <v>67</v>
+      <c r="A23" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24">
-        <v>750</v>
+      <c r="E24" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25">
-        <v>1300</v>
+        <v>22</v>
+      </c>
+      <c r="D25" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E26" t="s">
-        <v>67</v>
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27">
-        <v>1600</v>
-      </c>
-      <c r="E27" t="s">
-        <v>68</v>
+        <v>46</v>
+      </c>
+      <c r="D27" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28">
-        <v>750</v>
-      </c>
       <c r="E28" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29">
-        <v>330</v>
-      </c>
-      <c r="E29" t="s">
-        <v>68</v>
+        <v>28</v>
+      </c>
+      <c r="D29" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30">
-        <v>220</v>
-      </c>
-      <c r="E30" t="s">
-        <v>68</v>
+        <v>71</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" t="s">
+        <v>119</v>
+      </c>
+      <c r="E35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" t="s">
+        <v>120</v>
+      </c>
+      <c r="E36" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
         <v>61</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C37" t="s">
         <v>62</v>
       </c>
-      <c r="C31" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31">
-        <v>520</v>
-      </c>
-      <c r="E31" t="s">
-        <v>68</v>
+      <c r="D37" t="s">
+        <v>121</v>
+      </c>
+      <c r="E37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" t="s">
+        <v>117</v>
+      </c>
+      <c r="E38" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" t="s">
+        <v>117</v>
+      </c>
+      <c r="E39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" t="s">
+        <v>114</v>
+      </c>
+      <c r="E40" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" t="s">
+        <v>114</v>
+      </c>
+      <c r="E41" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E18" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A28:D30">
-    <sortCondition ref="D28:D30"/>
+  <autoFilter ref="A1:E25" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A34:D36">
+    <sortCondition ref="D34:D36"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="B13" r:id="rId1" xr:uid="{500C5F17-CD73-4F5C-9DAB-95952E174299}"/>
-    <hyperlink ref="C25" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
-    <hyperlink ref="C24" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
+    <hyperlink ref="B22" r:id="rId1" xr:uid="{500C5F17-CD73-4F5C-9DAB-95952E174299}"/>
+    <hyperlink ref="C30" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
+    <hyperlink ref="C29" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{ff6dbec8-95a8-4638-9f5f-bd076536645c}" enabled="1" method="Standard" siteId="{5dbf1add-202a-4b8d-815b-bf0fb024e033}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/extra-wishlist.xlsx
+++ b/extra-wishlist.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506A20C0-5A7A-4C5A-B5B8-F2B902A2B820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363C9961-8DEB-415D-A609-D8D8F8249C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="28995" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Extra Wishlist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="137">
   <si>
     <t>Image</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Reserved / bought</t>
-  </si>
-  <si>
     <t>Fujifilm X100VI</t>
   </si>
   <si>
@@ -242,9 +239,6 @@
     <t>GAP</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>https://www.digitec.ch/en/s1/product/voigtlaender-macro-apo-lanthar-65-mm-20-sony-e-full-size-lenses-11920971</t>
   </si>
   <si>
@@ -414,6 +408,48 @@
   </si>
   <si>
     <t>https://static01.galaxus.com/productimages/5/6/5/6/4/4/1/6/1/8/4/0/4/2/2/5/3/6/3/aa1c795f-247e-4e96-9a96-bdded01c865b_cropped.jpg_2880.avif</t>
+  </si>
+  <si>
+    <t>SKIP</t>
+  </si>
+  <si>
+    <t>SKIP (skip: hide from display) / Y (reserved: show faded out) / GAP (formatting gap)</t>
+  </si>
+  <si>
+    <t>8bitdo Arcade Stick</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/5/3/0/9/6/9/3/2/6/2/6/1/6/3/8/8/2/1/6/e9b3a391-deba-4043-bcc4-49ae473ffb8e.jpg_2880.avif</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/8bitdo-arcade-stick-switch-lite-switch-pc-game-controllers-13747515</t>
+  </si>
+  <si>
+    <t>78.60 CHF</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/-/en/World-Warcraft-Midnight-Collectors/dp/B0FSLM3998</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71ig+f21UKL._SL1500_.jpg</t>
+  </si>
+  <si>
+    <t>127 EUR</t>
+  </si>
+  <si>
+    <t>World of Warcraft: Midnight Collector's Edition</t>
+  </si>
+  <si>
+    <t>Sony Alpha 7 V</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/7/3/5/2/1/8/2/0/8/8/0/8/9/6/8/5/6/9/7/019ae408-e598-7593-824f-af1b3405f33d_2880.avif</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/sony-alpha-7-v-33-mpx-full-frame-cameras-65367350</t>
+  </si>
+  <si>
+    <t>2599 CHF</t>
   </si>
 </sst>
 </file>
@@ -795,12 +831,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.140625" customWidth="1"/>
     <col min="3" max="3" width="53.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="79" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -817,524 +854,572 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>4</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>88</v>
+      <c r="E4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E5" t="s">
-        <v>66</v>
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" t="s">
-        <v>74</v>
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E8" t="s">
-        <v>66</v>
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
+        <v>68</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E10" t="s">
-        <v>66</v>
+      <c r="A10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
+        <v>55</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" t="s">
-        <v>91</v>
+      <c r="E12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" t="s">
-        <v>94</v>
+        <v>17</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" t="s">
         <v>106</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D15" t="s">
         <v>107</v>
-      </c>
-      <c r="C14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E15" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
+        <v>20</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="3">
-        <v>160</v>
+        <v>23</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" t="s">
-        <v>104</v>
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="3">
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" t="s">
-        <v>65</v>
+        <v>43</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>98</v>
+        <v>120</v>
+      </c>
+      <c r="B23" t="s">
+        <v>121</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E24" t="s">
-        <v>66</v>
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>22</v>
+        <v>126</v>
+      </c>
+      <c r="C25" t="s">
+        <v>127</v>
       </c>
       <c r="D25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" t="s">
+        <v>94</v>
+      </c>
+      <c r="E31" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E28" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="1" t="s">
+      <c r="E34" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" t="s">
+        <v>110</v>
+      </c>
+      <c r="E35" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D30" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>122</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="B36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" t="s">
+        <v>117</v>
+      </c>
+      <c r="E36" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D31" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E32" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" t="s">
+    </row>
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" t="s">
         <v>118</v>
       </c>
-      <c r="E33" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" t="s">
-        <v>112</v>
-      </c>
-      <c r="E34" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="E37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" t="s">
         <v>119</v>
       </c>
-      <c r="E35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" t="s">
-        <v>120</v>
-      </c>
-      <c r="E36" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>60</v>
-      </c>
-      <c r="B37" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" t="s">
-        <v>62</v>
-      </c>
-      <c r="D37" t="s">
-        <v>121</v>
-      </c>
-      <c r="E37" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="E38" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" t="s">
         <v>49</v>
-      </c>
-      <c r="B38" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" t="s">
-        <v>117</v>
-      </c>
-      <c r="E38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" t="s">
-        <v>51</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E39" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" t="s">
         <v>35</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C41" t="s">
         <v>36</v>
       </c>
-      <c r="C40" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" t="s">
-        <v>114</v>
-      </c>
-      <c r="E40" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" t="s">
-        <v>43</v>
-      </c>
       <c r="D41" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E25" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A34:D36">
-    <sortCondition ref="D34:D36"/>
+  <autoFilter ref="A1:E43" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
+    <filterColumn colId="4">
+      <filters blank="1">
+        <filter val="GAP"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A35:D37">
+    <sortCondition ref="D35:D37"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="B22" r:id="rId1" xr:uid="{500C5F17-CD73-4F5C-9DAB-95952E174299}"/>
-    <hyperlink ref="C30" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
-    <hyperlink ref="C29" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
+    <hyperlink ref="B9" r:id="rId1" xr:uid="{500C5F17-CD73-4F5C-9DAB-95952E174299}"/>
+    <hyperlink ref="C22" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
+    <hyperlink ref="C21" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>

--- a/extra-wishlist.xlsx
+++ b/extra-wishlist.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363C9961-8DEB-415D-A609-D8D8F8249C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="6_{75CE9BD5-2DE1-477B-B485-D999B45B708C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B38D2E7-E445-45E1-84B8-EAA3D608F01A}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="28995" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="-28920" yWindow="7545" windowWidth="29040" windowHeight="16440" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Extra Wishlist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="142">
   <si>
     <t>Image</t>
   </si>
@@ -89,15 +89,6 @@
     <t>https://www.digitec.ch/en/s1/product/sony-alpha-7rv-61-mpx-full-frame-cameras-22823231</t>
   </si>
   <si>
-    <t>Apple iPad Air 11 2025 (M3)</t>
-  </si>
-  <si>
-    <t>https://static01.galaxus.com/productimages/1/9/1/3/1/6/9/0/2/7/6/0/5/5/9/9/7/1/56e6de25-8e03-4f19-b997-d12d17f2a578_cropped.jpg_720.avif</t>
-  </si>
-  <si>
-    <t>https://www.digitec.ch/en/s1/product/apple-ipad-air-11-2025-m3-wlan-only-11-256-gb-space-grey-tablets-55620779</t>
-  </si>
-  <si>
     <t>Synology DS923+</t>
   </si>
   <si>
@@ -152,15 +143,6 @@
     <t>https://www.lego.com/en-ch/product/boutique-hotel-10297</t>
   </si>
   <si>
-    <t>CITY OF DARKNESS – SPECIAL REPRINT</t>
-  </si>
-  <si>
-    <t>https://pictures.abebooks.com/isbn/9781873200896-us.jpg</t>
-  </si>
-  <si>
-    <t>https://www.abebooks.com/City-Darkness-Limited-Edition-Life-Kowloon/31292330335/bd</t>
-  </si>
-  <si>
     <t>LEGO 10350 Tudor Corner</t>
   </si>
   <si>
@@ -299,9 +281,6 @@
     <t>400 CHF</t>
   </si>
   <si>
-    <t>700 CHF</t>
-  </si>
-  <si>
     <t>Cullmann Carvao 816TCS</t>
   </si>
   <si>
@@ -335,24 +314,12 @@
     <t>https://www.digitec.ch/en/s1/product/sony-fe-100mm-f28-macro-gm-sony-e-full-size-lenses-62486907</t>
   </si>
   <si>
-    <t>1500 CHF</t>
-  </si>
-  <si>
-    <t>1020 CHF</t>
-  </si>
-  <si>
-    <t>870 CHF</t>
-  </si>
-  <si>
     <t>1236 CHF</t>
   </si>
   <si>
     <t>3800 CHF</t>
   </si>
   <si>
-    <t>1160 CHF</t>
-  </si>
-  <si>
     <t>Anker Prime</t>
   </si>
   <si>
@@ -450,15 +417,60 @@
   </si>
   <si>
     <t>2599 CHF</t>
+  </si>
+  <si>
+    <t>1056 CHF</t>
+  </si>
+  <si>
+    <t>838 CHF</t>
+  </si>
+  <si>
+    <t>1349 CHF</t>
+  </si>
+  <si>
+    <t>Zeiss Batis 18mm 2.8 E-Mount AF</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/3/4/6/9/4/1/6/3/6/5/0/8/6/4/7/8/2/2/0/019b1efe-7679-78c0-84dd-e9ff5b9d9f13_2880.avif</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/zeiss-batis-18mm-28-e-mount-af-sony-e-full-size-lenses-5748882</t>
+  </si>
+  <si>
+    <t>975 CHF</t>
+  </si>
+  <si>
+    <t>949 CHF</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/dji-osmo-mobile-8-smartphone-030-kg-gimbal-62918600</t>
+  </si>
+  <si>
+    <t>106 CHF</t>
+  </si>
+  <si>
+    <t>DJI Osmo Mobile 8</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/7/6/0/2/5/4/9/9/5/7/7/7/3/3/2/7/2/8/6/019bd8b9-2122-70de-80f2-4caba837a61f_2880.avif</t>
+  </si>
+  <si>
+    <t>https://www.apple.com/ch-fr/shop/buy-ipad/ipad-air/ecran-11-pouces-256go-gris-sid%C3%A9ral-wifi</t>
+  </si>
+  <si>
+    <t>https://store.storeimages.cdn-apple.com/1/as-images.apple.com/is/ipad-air-payment-apple-care-plus-summary-202405-11inch-space-gray-wifi?wid=5120&amp;hei=2880&amp;fmt=webp&amp;qlt=90&amp;.v=Z0oxM0ZGMy9IV1pMQ3NweHNXMWo1SGpyV1dNeExxTyt6ck93V1p1bnUxTDkzNjR4cXlXWEpkZW82c1hYaGdudktVVm9GOEYvV3M1Vm4yWFhRQzBCQTREbHQ5eENKOEJWbHZEOHJPdFRrc2NFOXNkRmE2NjMrR1FyMzdLUFNST0ZYN29lZ3JTYXorZWFSSjRsbElpVUp5SXB2b0VJREc1eXF4NDd1SlU3TC9Z&amp;traceId=1</t>
+  </si>
+  <si>
+    <t>679 CHF</t>
+  </si>
+  <si>
+    <t>Apple iPad Air 11" WiFi 256</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -511,11 +523,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -532,6 +543,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -832,7 +847,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.140625" customWidth="1"/>
@@ -854,575 +869,593 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" t="s">
+        <v>120</v>
+      </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E4" t="s">
-        <v>65</v>
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" t="s">
-        <v>135</v>
+        <v>49</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
+        <v>88</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>62</v>
       </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
+      <c r="B8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" t="s">
-        <v>99</v>
+      <c r="E9" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>97</v>
+        <v>136</v>
+      </c>
+      <c r="B10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" t="s">
+        <v>134</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>54</v>
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E12" t="s">
-        <v>65</v>
+      <c r="A12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" t="s">
-        <v>86</v>
+      <c r="E13" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
+        <v>37</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
-      </c>
-      <c r="C15" t="s">
-        <v>106</v>
+        <v>23</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E18" t="s">
-        <v>65</v>
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="3">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="D19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
+      </c>
+      <c r="C20" t="s">
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="E20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>27</v>
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="E21" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>70</v>
+        <v>52</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="E22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>108</v>
+        <v>81</v>
+      </c>
+      <c r="C23" t="s">
+        <v>83</v>
       </c>
       <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" t="s">
-        <v>41</v>
-      </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="E24" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" t="s">
-        <v>127</v>
+        <v>14</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>92</v>
+      </c>
+      <c r="E25" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E26" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
+        <v>5</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" t="s">
-        <v>77</v>
+        <v>8</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="E28" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" t="s">
-        <v>56</v>
+        <v>27</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D29" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="E29" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="E30" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D32" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E32" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" t="s">
+        <v>104</v>
+      </c>
       <c r="E33" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>6</v>
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E34" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E35" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>29</v>
+        <v>57</v>
+      </c>
+      <c r="C36" t="s">
+        <v>58</v>
       </c>
       <c r="D36" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="E36" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="E37" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" t="s">
-        <v>61</v>
+        <v>17</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="E38" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E39" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" t="s">
-        <v>115</v>
-      </c>
-      <c r="E40" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" t="s">
-        <v>36</v>
-      </c>
-      <c r="D41" t="s">
-        <v>112</v>
-      </c>
-      <c r="E41" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E43" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
+  <autoFilter ref="A1:E35" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
     <filterColumn colId="4">
       <filters blank="1">
         <filter val="GAP"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A35:D37">
-    <sortCondition ref="D35:D37"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A28:D30">
+    <sortCondition ref="D28:D30"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="B9" r:id="rId1" xr:uid="{500C5F17-CD73-4F5C-9DAB-95952E174299}"/>
-    <hyperlink ref="C22" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
-    <hyperlink ref="C21" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{500C5F17-CD73-4F5C-9DAB-95952E174299}"/>
+    <hyperlink ref="C16" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
+    <hyperlink ref="C15" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
+    <hyperlink ref="C39" r:id="rId4" xr:uid="{70AAF641-556E-4186-A150-1E8C658BA2FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 

--- a/extra-wishlist.xlsx
+++ b/extra-wishlist.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="6_{75CE9BD5-2DE1-477B-B485-D999B45B708C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B38D2E7-E445-45E1-84B8-EAA3D608F01A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D664F4-3EEE-407E-AED6-119C200FF399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="7545" windowWidth="29040" windowHeight="16440" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Extra Wishlist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$48</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="176">
   <si>
     <t>Image</t>
   </si>
@@ -89,9 +89,6 @@
     <t>https://www.digitec.ch/en/s1/product/sony-alpha-7rv-61-mpx-full-frame-cameras-22823231</t>
   </si>
   <si>
-    <t>Synology DS923+</t>
-  </si>
-  <si>
     <t>https://static01.galaxus.com/productimages/3/6/3/4/3/0/7/0/5/5/9/8/3/8/0/5/9/0/9/1a5b9310-192f-4565-8e87-b6a9163262f9_cropped.jpg_2880.avif</t>
   </si>
   <si>
@@ -461,10 +458,115 @@
     <t>https://store.storeimages.cdn-apple.com/1/as-images.apple.com/is/ipad-air-payment-apple-care-plus-summary-202405-11inch-space-gray-wifi?wid=5120&amp;hei=2880&amp;fmt=webp&amp;qlt=90&amp;.v=Z0oxM0ZGMy9IV1pMQ3NweHNXMWo1SGpyV1dNeExxTyt6ck93V1p1bnUxTDkzNjR4cXlXWEpkZW82c1hYaGdudktVVm9GOEYvV3M1Vm4yWFhRQzBCQTREbHQ5eENKOEJWbHZEOHJPdFRrc2NFOXNkRmE2NjMrR1FyMzdLUFNST0ZYN29lZ3JTYXorZWFSSjRsbElpVUp5SXB2b0VJREc1eXF4NDd1SlU3TC9Z&amp;traceId=1</t>
   </si>
   <si>
-    <t>679 CHF</t>
-  </si>
-  <si>
     <t>Apple iPad Air 11" WiFi 256</t>
+  </si>
+  <si>
+    <t>Anker MagGo</t>
+  </si>
+  <si>
+    <t>https://www.smallrig.com/eu/smallrig-Advanced-Cage-Kit-for-Sony-Alpha-7R-V-Alpha-7IV-Alpha-7SIII-3669C.html</t>
+  </si>
+  <si>
+    <t>157.90 EUR</t>
+  </si>
+  <si>
+    <t>GoPro Fluid Pro AI</t>
+  </si>
+  <si>
+    <t>147 CHF</t>
+  </si>
+  <si>
+    <t>https://static.smallrig.com/mall/img/public/uhx81pr7woj-1769484760951_.JPG</t>
+  </si>
+  <si>
+    <t>Advanced Cage Kit for Sony A7 V</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/anker-prime-26250-mah-140-w-9975-wh-powerbanks-65413077</t>
+  </si>
+  <si>
+    <t>150 CHF</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/4/5/3/5/9/9/5/1/2/3/3/5/9/0/8/5/8/5/0/019eefe7-51f1-7838-955a-600006c0637e_2880.avif</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/synology-ds925-0-tb-nas-57572371</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/5/5/2/2/1/6/4/0/1/6/2/7/0/3/8/3/2/4/7/0196aa58-bfbd-7099-b675-8ba0aba868dd_720.avif</t>
+  </si>
+  <si>
+    <t>624 CHF</t>
+  </si>
+  <si>
+    <t>Synology DS925+</t>
+  </si>
+  <si>
+    <t>48 CHF</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/5/5/7/2/8/7/5/9/8/2/0/1/4/2/5/8/3/3/7/01a005b6-019c-76e8-852b-2e2ec1451d9f_720.avif</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/anker-maggo-10000-mah-30-w-37-wh-powerbanks-52379096</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/1/1/4/9/7/3/0/0/5/9/4/8/1/2/1/3/5/0/6/019a267c-c52a-7e01-b9f8-c15e936c5316_1000.avif</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/peak-design-everyday-sling-camera-shoulder-bag-6-l-camera-bag-60670840</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/3/0/5/0/4/0/6/4/0/3/2/9/6/9/5/2/7/8/4/019b149b-1fed-7cdd-9097-e23b3c7c18e8_1000.avif</t>
+  </si>
+  <si>
+    <t>129 CHF</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/angelbird-av-pro-cfexpress-a-512-gb-cfexpress-type-a-memory-card-53079011</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/2/9/0/1/0/6/9/0/7/2/7/4/9/7/7/1/1/3/4/019f36ea-ba7b-7f52-bbfb-550102789812_720.avif</t>
+  </si>
+  <si>
+    <t>Angelbird AV PRO CFexpress A</t>
+  </si>
+  <si>
+    <t>317 CHF</t>
+  </si>
+  <si>
+    <t>Viltrox TC-2.0X</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/viltrox-tc-20x-teleconverter-sony-e-lens-converters-65258332</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/7/1/8/3/5/6/8/2/5/6/4/5/8/9/3/4/7/1/4/019fd891-aec4-707c-bd58-2db99d989135_720.avif</t>
+  </si>
+  <si>
+    <t>213 CHF</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/3/8/1/4/2/9/7/0/7/9/0/7/0/2/3/0/8/8/1/019fff90-e797-7ea0-a0a4-4d9766c46cb8_720.avif</t>
+  </si>
+  <si>
+    <t>500 CHF</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/gopro-fluid-pro-ai-action-camera-accessories-62789615</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/9/1/0/7/4/3/5/9/2/5/1/8/7/4/2/3/6/6/3/0199c167-391c-722c-829a-264bde77f898_720.avif</t>
+  </si>
+  <si>
+    <t>829 CHF</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Geanta</t>
   </si>
 </sst>
 </file>
@@ -543,10 +645,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -847,11 +945,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.140625" customWidth="1"/>
     <col min="3" max="3" width="53.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="79" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -869,590 +968,749 @@
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>121</v>
       </c>
-      <c r="B2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>122</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>123</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>124</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>46</v>
       </c>
-      <c r="B4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>129</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>130</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>131</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" t="s">
-        <v>133</v>
+      <c r="E8" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E9" t="s">
-        <v>59</v>
+      <c r="A9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" t="s">
+        <v>141</v>
+      </c>
+      <c r="D9" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E13" t="s">
-        <v>59</v>
+      <c r="A13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D13" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>39</v>
+        <v>155</v>
+      </c>
+      <c r="C14" t="s">
+        <v>156</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>163</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>24</v>
+        <v>162</v>
+      </c>
+      <c r="C15" t="s">
+        <v>161</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>167</v>
+      </c>
+      <c r="C16" t="s">
+        <v>166</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>97</v>
+        <v>157</v>
+      </c>
+      <c r="C17" t="s">
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>175</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="D20" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="E20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" t="s">
-        <v>79</v>
-      </c>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E22" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>83</v>
+        <v>36</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" t="s">
-        <v>85</v>
+        <v>22</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" t="s">
+        <v>77</v>
+      </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
+      </c>
+      <c r="C27" t="s">
+        <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E27" t="s">
-        <v>112</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>113</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>9</v>
+        <v>114</v>
+      </c>
+      <c r="C28" t="s">
+        <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="E28" t="s">
-        <v>112</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>26</v>
+        <v>72</v>
+      </c>
+      <c r="C29" t="s">
+        <v>65</v>
       </c>
       <c r="D29" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="E29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="E30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>41</v>
+        <v>80</v>
+      </c>
+      <c r="C32" t="s">
+        <v>82</v>
       </c>
       <c r="D32" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="E32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>40</v>
+        <v>83</v>
+      </c>
+      <c r="C33" t="s">
+        <v>84</v>
       </c>
       <c r="D33" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>91</v>
+      </c>
+      <c r="E34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" t="s">
+        <v>104</v>
+      </c>
+      <c r="E36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D38" t="s">
+        <v>105</v>
+      </c>
+      <c r="E38" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" t="s">
+        <v>106</v>
+      </c>
+      <c r="E39" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" t="s">
+        <v>54</v>
+      </c>
+      <c r="D40" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" t="s">
+        <v>103</v>
+      </c>
+      <c r="E42" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B43" t="s">
         <v>31</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C43" t="s">
         <v>32</v>
       </c>
-      <c r="C34" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="D43" t="s">
+        <v>100</v>
+      </c>
+      <c r="E43" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
+        <v>77</v>
+      </c>
+      <c r="E44" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" t="s">
+        <v>90</v>
+      </c>
+      <c r="E45" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" t="s">
+        <v>94</v>
+      </c>
+      <c r="D46" t="s">
+        <v>95</v>
+      </c>
+      <c r="E46" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" t="s">
+        <v>102</v>
+      </c>
+      <c r="E47" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" t="s">
         <v>101</v>
       </c>
-      <c r="E34" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" t="s">
-        <v>78</v>
-      </c>
-      <c r="E35" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" t="s">
-        <v>91</v>
-      </c>
-      <c r="E36" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" t="s">
-        <v>96</v>
-      </c>
-      <c r="E37" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38" t="s">
-        <v>103</v>
-      </c>
-      <c r="E38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>19</v>
-      </c>
-      <c r="B39" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D39" t="s">
-        <v>102</v>
-      </c>
-      <c r="E39" t="s">
-        <v>112</v>
+      <c r="E48" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E35" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
+  <autoFilter ref="A1:E48" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
     <filterColumn colId="4">
       <filters blank="1">
         <filter val="GAP"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A28:D30">
-    <sortCondition ref="D28:D30"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A37:D39">
+    <sortCondition ref="D37:D39"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{500C5F17-CD73-4F5C-9DAB-95952E174299}"/>
-    <hyperlink ref="C16" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
-    <hyperlink ref="C15" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
-    <hyperlink ref="C39" r:id="rId4" xr:uid="{70AAF641-556E-4186-A150-1E8C658BA2FE}"/>
+    <hyperlink ref="C25" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
+    <hyperlink ref="C24" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
+    <hyperlink ref="C48" r:id="rId4" xr:uid="{70AAF641-556E-4186-A150-1E8C658BA2FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>

--- a/extra-wishlist.xlsx
+++ b/extra-wishlist.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D664F4-3EEE-407E-AED6-119C200FF399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{67D664F4-3EEE-407E-AED6-119C200FF399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7F65953-CB56-4CC1-9153-B6BA0299C6E7}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11452" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Extra Wishlist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="178">
   <si>
     <t>Image</t>
   </si>
@@ -567,6 +567,12 @@
   </si>
   <si>
     <t>Geanta</t>
+  </si>
+  <si>
+    <t>Macro Flash Kit</t>
+  </si>
+  <si>
+    <t>TBD</t>
   </si>
 </sst>
 </file>
@@ -945,16 +951,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E49"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="26.140625" customWidth="1"/>
-    <col min="3" max="3" width="53.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="26.1328125" customWidth="1"/>
+    <col min="3" max="3" width="53.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="79" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -971,7 +977,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>120</v>
       </c>
@@ -988,7 +994,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>121</v>
       </c>
@@ -1005,7 +1011,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -1022,7 +1028,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -1039,7 +1045,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -1056,7 +1062,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>128</v>
       </c>
@@ -1073,7 +1079,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>61</v>
       </c>
@@ -1090,7 +1096,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>146</v>
       </c>
@@ -1104,493 +1110,490 @@
         <v>142</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>143</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>172</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>171</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
         <v>61</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>169</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
         <v>92</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>149</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>147</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
         <v>153</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>151</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>150</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
         <v>140</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>155</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>156</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
         <v>163</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>162</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>161</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
         <v>165</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>167</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>166</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
         <v>73</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>157</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>75</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
         <v>175</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>159</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C19" t="s">
         <v>158</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D19" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
         <v>139</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>138</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>137</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
         <v>135</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>136</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>133</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D21" t="s">
         <v>134</v>
       </c>
-      <c r="E20" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="E21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
         <v>73</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>74</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>75</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D22" t="s">
         <v>76</v>
       </c>
-      <c r="E21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E23" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
         <v>37</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
         <v>21</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
         <v>64</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
         <v>108</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>77</v>
       </c>
-      <c r="E26" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="E27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
         <v>33</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>34</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>35</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>100</v>
-      </c>
-      <c r="E27" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>113</v>
-      </c>
-      <c r="B28" t="s">
-        <v>114</v>
-      </c>
-      <c r="C28" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" t="s">
-        <v>116</v>
       </c>
       <c r="E28" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
         <v>68</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>72</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" t="s">
         <v>65</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>66</v>
       </c>
-      <c r="E29" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="E30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
         <v>67</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>69</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>70</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>71</v>
       </c>
-      <c r="E30" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="E31" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
         <v>50</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>51</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" t="s">
         <v>49</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D32" t="s">
         <v>78</v>
       </c>
-      <c r="E31" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="E32" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
         <v>79</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>80</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>82</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>81</v>
       </c>
-      <c r="E32" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="E33" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
         <v>85</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>83</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>84</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>86</v>
       </c>
-      <c r="E33" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="E34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
         <v>13</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D35" t="s">
         <v>91</v>
       </c>
-      <c r="E34" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E35" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E36" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
         <v>4</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D37" t="s">
         <v>104</v>
       </c>
-      <c r="E36" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="E37" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
         <v>7</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D38" t="s">
         <v>98</v>
       </c>
-      <c r="E37" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="E38" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
         <v>24</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>26</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D39" t="s">
         <v>105</v>
       </c>
-      <c r="E38" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="E39" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
         <v>27</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>28</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C40" t="s">
         <v>29</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D40" t="s">
         <v>106</v>
       </c>
-      <c r="E39" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="E40" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
         <v>52</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>53</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C41" t="s">
         <v>54</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>107</v>
       </c>
-      <c r="E40" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D41" t="s">
-        <v>103</v>
-      </c>
       <c r="E41" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D42" t="s">
         <v>103</v>
@@ -1599,118 +1602,135 @@
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" t="s">
+        <v>103</v>
+      </c>
+      <c r="E43" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
         <v>30</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>31</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C44" t="s">
         <v>32</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D44" t="s">
         <v>100</v>
       </c>
-      <c r="E43" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="E44" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
         <v>10</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D45" t="s">
         <v>77</v>
       </c>
-      <c r="E44" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="E45" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
         <v>55</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>56</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C46" t="s">
         <v>57</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D46" t="s">
         <v>90</v>
       </c>
-      <c r="E45" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B46" t="s">
+      <c r="E46" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
         <v>93</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>94</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>95</v>
       </c>
-      <c r="E46" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B47" t="s">
+      <c r="E47" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" t="s">
         <v>102</v>
       </c>
-      <c r="E47" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="E48" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
         <v>18</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" t="s">
         <v>19</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>101</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E49" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E48" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
+  <autoFilter ref="A1:E49" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
     <filterColumn colId="4">
       <filters blank="1">
         <filter val="GAP"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A37:D39">
-    <sortCondition ref="D37:D39"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A38:D40">
+    <sortCondition ref="D38:D40"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{500C5F17-CD73-4F5C-9DAB-95952E174299}"/>
-    <hyperlink ref="C25" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
-    <hyperlink ref="C24" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
-    <hyperlink ref="C48" r:id="rId4" xr:uid="{70AAF641-556E-4186-A150-1E8C658BA2FE}"/>
+    <hyperlink ref="C26" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
+    <hyperlink ref="C25" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
+    <hyperlink ref="C49" r:id="rId4" xr:uid="{70AAF641-556E-4186-A150-1E8C658BA2FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
